--- a/docs/test/unit/NOUS-102/観点表_generationConfig.xlsx
+++ b/docs/test/unit/NOUS-102/観点表_generationConfig.xlsx
@@ -2651,7 +2651,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 2：weights がすべて 0 の設定も検証を通る。このとき候補の抽選は ['post'] を返す（観点表_gate_candidates_rng の TC-UT_CAND-014）。起動時に弾くかどうかは設計書に記載がない。</t>
+          <t>・確認事項 2（決定済み）：weights がすべて 0 の設定も検証を通る。このとき候補の抽選は ['post'] を返す（観点表_gate_candidates_rng の TC-UT_CAND-014）。設定ファイルは開発側が書くため起動時に弾かず、この動きを仕様とする（2026-10-23 NOUS-102 で Kouhei Tajima が決定）。</t>
         </is>
       </c>
     </row>
